--- a/e2e/fixtures/new-format/error-49-kids.xlsx
+++ b/e2e/fixtures/new-format/error-49-kids.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/darren/Projects/NY-Sheriff-Summer-Camp-Scheduler/e2e/fixtures/new-format/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D2C9E96-C8EB-384B-B639-E694F946CB72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B026732A-4310-654F-81D4-F79D2518A580}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="44800" windowHeight="25200" firstSheet="1" activeTab="1" xr2:uid="{B75E9CFD-F73C-4E0E-B330-6F712BC21BE5}"/>
   </bookViews>
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3178" uniqueCount="1080">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3179" uniqueCount="1080">
   <si>
     <t>Otsego</t>
   </si>
@@ -9427,7 +9427,9 @@
       <c r="AT28" s="26" t="s">
         <v>257</v>
       </c>
-      <c r="AU28" s="26"/>
+      <c r="AU28" s="26" t="s">
+        <v>148</v>
+      </c>
       <c r="AV28" s="26" t="s">
         <v>149</v>
       </c>
